--- a/Baptiste_territory_chart.xlsx
+++ b/Baptiste_territory_chart.xlsx
@@ -8,181 +8,61 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danielbaptiste\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009F57AE-1BD8-4F50-B093-3FE9591B8382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{456F7A22-1771-4011-B45F-DC075DFD8891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="1360" windowWidth="14400" windowHeight="8170" xr2:uid="{CE5F9FAF-BB32-4DB8-8851-1033B0EC0545}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CB467266-7350-466E-B6F2-2B56458F12B4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pivot Chart" sheetId="3" r:id="rId1"/>
+    <sheet name="Pivot Chart" sheetId="2" r:id="rId1"/>
     <sheet name="BAPTISTECSV" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="3" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
-    <t>Sales_Month</t>
+    <t>StoreLocation</t>
   </si>
   <si>
-    <t>Monthly_Sales</t>
+    <t>New London</t>
   </si>
   <si>
-    <t>2022-01</t>
+    <t>Bridgeport</t>
   </si>
   <si>
-    <t>2022-02</t>
+    <t>Hartford</t>
   </si>
   <si>
-    <t>2022-03</t>
+    <t>Waterbury</t>
   </si>
   <si>
-    <t>2022-04</t>
+    <t>New Haven</t>
   </si>
   <si>
-    <t>2022-05</t>
+    <t>Litchfield County</t>
   </si>
   <si>
-    <t>2022-06</t>
+    <t>Darien</t>
   </si>
   <si>
-    <t>2022-07</t>
+    <t>Old Saybrook</t>
   </si>
   <si>
-    <t>2022-08</t>
+    <t>Total Sales</t>
   </si>
   <si>
-    <t>2022-09</t>
-  </si>
-  <si>
-    <t>2022-10</t>
-  </si>
-  <si>
-    <t>2022-11</t>
-  </si>
-  <si>
-    <t>2022-12</t>
-  </si>
-  <si>
-    <t>2023-01</t>
-  </si>
-  <si>
-    <t>2023-02</t>
-  </si>
-  <si>
-    <t>2023-03</t>
-  </si>
-  <si>
-    <t>2023-04</t>
-  </si>
-  <si>
-    <t>2023-05</t>
-  </si>
-  <si>
-    <t>2023-06</t>
-  </si>
-  <si>
-    <t>2023-07</t>
-  </si>
-  <si>
-    <t>2023-08</t>
-  </si>
-  <si>
-    <t>2023-09</t>
-  </si>
-  <si>
-    <t>2023-10</t>
-  </si>
-  <si>
-    <t>2023-11</t>
-  </si>
-  <si>
-    <t>2023-12</t>
-  </si>
-  <si>
-    <t>2024-01</t>
-  </si>
-  <si>
-    <t>2024-02</t>
-  </si>
-  <si>
-    <t>2024-03</t>
-  </si>
-  <si>
-    <t>2024-04</t>
-  </si>
-  <si>
-    <t>2024-05</t>
-  </si>
-  <si>
-    <t>2024-06</t>
-  </si>
-  <si>
-    <t>2024-07</t>
-  </si>
-  <si>
-    <t>2024-08</t>
-  </si>
-  <si>
-    <t>2024-09</t>
-  </si>
-  <si>
-    <t>2024-10</t>
-  </si>
-  <si>
-    <t>2024-11</t>
-  </si>
-  <si>
-    <t>2024-12</t>
-  </si>
-  <si>
-    <t>2025-01</t>
-  </si>
-  <si>
-    <t>2025-02</t>
-  </si>
-  <si>
-    <t>2025-03</t>
-  </si>
-  <si>
-    <t>2025-04</t>
-  </si>
-  <si>
-    <t>2025-05</t>
-  </si>
-  <si>
-    <t>2025-06</t>
-  </si>
-  <si>
-    <t>2025-07</t>
-  </si>
-  <si>
-    <t>2025-08</t>
-  </si>
-  <si>
-    <t>2025-09</t>
-  </si>
-  <si>
-    <t>2025-10</t>
-  </si>
-  <si>
-    <t>2025-11</t>
-  </si>
-  <si>
-    <t>2025-12</t>
+    <t>Sum of Total Sales</t>
   </si>
   <si>
     <t>Row Labels</t>
   </si>
   <si>
     <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Sum of Monthly_Sales</t>
   </si>
 </sst>
 </file>
@@ -670,14 +550,20 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -724,7 +610,19 @@
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -755,7 +653,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Baptiste_territory_chart.xlsx]Pivot Chart!PivotTable3</c:name>
+    <c:name>[Baptiste_territory_chartNEW.xlsx]Pivot Chart!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -880,312 +778,72 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Chart'!$A$2:$A$50</c:f>
+              <c:f>'Pivot Chart'!$A$2:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="48"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2022-01</c:v>
+                  <c:v>Bridgeport</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022-02</c:v>
+                  <c:v>Darien</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2022-03</c:v>
+                  <c:v>Hartford</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2022-04</c:v>
+                  <c:v>Litchfield County</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2022-05</c:v>
+                  <c:v>New Haven</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2022-06</c:v>
+                  <c:v>New London</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2022-07</c:v>
+                  <c:v>Old Saybrook</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2022-08</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2022-09</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2022-10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2022-11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2022-12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2023-01</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2023-02</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2023-03</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2023-04</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2023-05</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2023-06</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2023-07</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2023-08</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2023-09</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2023-10</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2023-11</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2023-12</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2024-01</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2024-02</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2024-03</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2024-04</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2024-05</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2024-06</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2024-07</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2024-08</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2024-09</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2024-10</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2024-11</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2024-12</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2025-01</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2025-02</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2025-03</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2025-04</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2025-05</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2025-06</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2025-07</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2025-08</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2025-09</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2025-10</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2025-11</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2025-12</c:v>
+                  <c:v>Waterbury</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Chart'!$B$2:$B$50</c:f>
+              <c:f>'Pivot Chart'!$B$2:$B$10</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>29958.25</c:v>
+                  <c:v>322100.07</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25563.98</c:v>
+                  <c:v>283455.62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>33995.57</c:v>
+                  <c:v>309592.06</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31587.119999999999</c:v>
+                  <c:v>286217.15000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>37953.480000000003</c:v>
+                  <c:v>286779.43</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32008.85</c:v>
+                  <c:v>331116.76</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>30656.27</c:v>
+                  <c:v>277310.18</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>42881.99</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>30369.64</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>43646.37</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>25950.41</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>34680.639999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>38351.449999999997</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>53435.37</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>50828.54</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>45747.199999999997</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>39215.78</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>39754.07</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>49592.69</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>48445.34</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>49175.79</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>45347.65</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>42683.73</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>50446.82</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>57974.76</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>49206.33</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>46044.68</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>38918.300000000003</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>41203.81</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>48142.95</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>48445.34</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>49633.16</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>44890.28</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>43061.440000000002</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>50069.11</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>38351.449999999997</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>68601.89</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>55131.75</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>69261.429999999993</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>58288.72</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>66996.149999999994</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>60671.67</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>88590.03</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>77048.509999999995</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>71032.14</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>115828.46</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>59762.07</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>92791.01</c:v>
+                  <c:v>295651.17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6A90-49B7-958A-4F435E036164}"/>
+              <c16:uniqueId val="{00000000-75F4-475C-83E8-FE766F04D194}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1199,11 +857,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1258384752"/>
-        <c:axId val="1258378032"/>
+        <c:axId val="1661210415"/>
+        <c:axId val="1661232975"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1258384752"/>
+        <c:axId val="1661210415"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1246,7 +904,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1258378032"/>
+        <c:crossAx val="1661232975"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1254,7 +912,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1258378032"/>
+        <c:axId val="1661232975"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1274,7 +932,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1305,7 +963,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1258384752"/>
+        <c:crossAx val="1661210415"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1955,23 +1613,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>336550</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>311150</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>16510</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD6137B7-C4BF-3DB3-072A-37C157AE2810}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5777CFF8-3256-DA6C-1C54-A84A392432A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1993,65 +1651,26 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="daniel baptiste" refreshedDate="46141.454883796294" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{C997B390-6B02-40E2-99AB-06C2D664104F}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="daniel baptiste" refreshedDate="46141.93333472222" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="9" xr:uid="{E1F94E6A-4297-4E18-95A6-B19EA8090E82}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:B49" sheet="BAPTISTECSV"/>
+    <worksheetSource ref="A1:B1048576" sheet="BAPTISTECSV"/>
   </cacheSource>
   <cacheFields count="2">
-    <cacheField name="Sales_Month" numFmtId="0">
-      <sharedItems count="48">
-        <s v="2022-01"/>
-        <s v="2022-02"/>
-        <s v="2022-03"/>
-        <s v="2022-04"/>
-        <s v="2022-05"/>
-        <s v="2022-06"/>
-        <s v="2022-07"/>
-        <s v="2022-08"/>
-        <s v="2022-09"/>
-        <s v="2022-10"/>
-        <s v="2022-11"/>
-        <s v="2022-12"/>
-        <s v="2023-01"/>
-        <s v="2023-02"/>
-        <s v="2023-03"/>
-        <s v="2023-04"/>
-        <s v="2023-05"/>
-        <s v="2023-06"/>
-        <s v="2023-07"/>
-        <s v="2023-08"/>
-        <s v="2023-09"/>
-        <s v="2023-10"/>
-        <s v="2023-11"/>
-        <s v="2023-12"/>
-        <s v="2024-01"/>
-        <s v="2024-02"/>
-        <s v="2024-03"/>
-        <s v="2024-04"/>
-        <s v="2024-05"/>
-        <s v="2024-06"/>
-        <s v="2024-07"/>
-        <s v="2024-08"/>
-        <s v="2024-09"/>
-        <s v="2024-10"/>
-        <s v="2024-11"/>
-        <s v="2024-12"/>
-        <s v="2025-01"/>
-        <s v="2025-02"/>
-        <s v="2025-03"/>
-        <s v="2025-04"/>
-        <s v="2025-05"/>
-        <s v="2025-06"/>
-        <s v="2025-07"/>
-        <s v="2025-08"/>
-        <s v="2025-09"/>
-        <s v="2025-10"/>
-        <s v="2025-11"/>
-        <s v="2025-12"/>
+    <cacheField name="Total Sales" numFmtId="44">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="277310.18" maxValue="331116.76"/>
+    </cacheField>
+    <cacheField name="StoreLocation" numFmtId="0">
+      <sharedItems containsBlank="1" count="9">
+        <s v="New London"/>
+        <s v="Bridgeport"/>
+        <s v="Hartford"/>
+        <s v="Waterbury"/>
+        <s v="New Haven"/>
+        <s v="Litchfield County"/>
+        <s v="Darien"/>
+        <s v="Old Saybrook"/>
+        <m/>
       </sharedItems>
-    </cacheField>
-    <cacheField name="Monthly_Sales" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="25563.98" maxValue="115828.46"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -2063,265 +1682,70 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="48">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="9">
   <r>
+    <n v="331116.76"/>
     <x v="0"/>
-    <n v="29958.25"/>
   </r>
   <r>
+    <n v="322100.07"/>
     <x v="1"/>
-    <n v="25563.98"/>
   </r>
   <r>
+    <n v="309592.06"/>
     <x v="2"/>
-    <n v="33995.57"/>
   </r>
   <r>
+    <n v="295651.17"/>
     <x v="3"/>
-    <n v="31587.119999999999"/>
   </r>
   <r>
+    <n v="286779.43"/>
     <x v="4"/>
-    <n v="37953.480000000003"/>
   </r>
   <r>
+    <n v="286217.15000000002"/>
     <x v="5"/>
-    <n v="32008.85"/>
   </r>
   <r>
+    <n v="283455.62"/>
     <x v="6"/>
-    <n v="30656.27"/>
   </r>
   <r>
+    <n v="277310.18"/>
     <x v="7"/>
-    <n v="42881.99"/>
   </r>
   <r>
+    <m/>
     <x v="8"/>
-    <n v="30369.64"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <n v="43646.37"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <n v="25950.41"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <n v="34680.639999999999"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <n v="38351.449999999997"/>
-  </r>
-  <r>
-    <x v="13"/>
-    <n v="53435.37"/>
-  </r>
-  <r>
-    <x v="14"/>
-    <n v="50828.54"/>
-  </r>
-  <r>
-    <x v="15"/>
-    <n v="45747.199999999997"/>
-  </r>
-  <r>
-    <x v="16"/>
-    <n v="39215.78"/>
-  </r>
-  <r>
-    <x v="17"/>
-    <n v="39754.07"/>
-  </r>
-  <r>
-    <x v="18"/>
-    <n v="49592.69"/>
-  </r>
-  <r>
-    <x v="19"/>
-    <n v="48445.34"/>
-  </r>
-  <r>
-    <x v="20"/>
-    <n v="49175.79"/>
-  </r>
-  <r>
-    <x v="21"/>
-    <n v="45347.65"/>
-  </r>
-  <r>
-    <x v="22"/>
-    <n v="42683.73"/>
-  </r>
-  <r>
-    <x v="23"/>
-    <n v="50446.82"/>
-  </r>
-  <r>
-    <x v="24"/>
-    <n v="57974.76"/>
-  </r>
-  <r>
-    <x v="25"/>
-    <n v="49206.33"/>
-  </r>
-  <r>
-    <x v="26"/>
-    <n v="46044.68"/>
-  </r>
-  <r>
-    <x v="27"/>
-    <n v="38918.300000000003"/>
-  </r>
-  <r>
-    <x v="28"/>
-    <n v="41203.81"/>
-  </r>
-  <r>
-    <x v="29"/>
-    <n v="48142.95"/>
-  </r>
-  <r>
-    <x v="30"/>
-    <n v="48445.34"/>
-  </r>
-  <r>
-    <x v="31"/>
-    <n v="49633.16"/>
-  </r>
-  <r>
-    <x v="32"/>
-    <n v="44890.28"/>
-  </r>
-  <r>
-    <x v="33"/>
-    <n v="43061.440000000002"/>
-  </r>
-  <r>
-    <x v="34"/>
-    <n v="50069.11"/>
-  </r>
-  <r>
-    <x v="35"/>
-    <n v="38351.449999999997"/>
-  </r>
-  <r>
-    <x v="36"/>
-    <n v="68601.89"/>
-  </r>
-  <r>
-    <x v="37"/>
-    <n v="55131.75"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <n v="69261.429999999993"/>
-  </r>
-  <r>
-    <x v="39"/>
-    <n v="58288.72"/>
-  </r>
-  <r>
-    <x v="40"/>
-    <n v="66996.149999999994"/>
-  </r>
-  <r>
-    <x v="41"/>
-    <n v="60671.67"/>
-  </r>
-  <r>
-    <x v="42"/>
-    <n v="88590.03"/>
-  </r>
-  <r>
-    <x v="43"/>
-    <n v="77048.509999999995"/>
-  </r>
-  <r>
-    <x v="44"/>
-    <n v="71032.14"/>
-  </r>
-  <r>
-    <x v="45"/>
-    <n v="115828.46"/>
-  </r>
-  <r>
-    <x v="46"/>
-    <n v="59762.07"/>
-  </r>
-  <r>
-    <x v="47"/>
-    <n v="92791.01"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{869F9CD4-6D63-46A1-8DF0-019CC78672EE}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3EA36B0F-220A-4679-987F-9CE973E532A1}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A1:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
+    <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="49">
+      <items count="10">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="4"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
+        <item x="7"/>
         <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
+        <item h="1" x="8"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="0"/>
+    <field x="1"/>
   </rowFields>
-  <rowItems count="49">
+  <rowItems count="9">
     <i>
       <x/>
     </i>
@@ -2346,126 +1770,6 @@
     <i>
       <x v="7"/>
     </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i>
-      <x v="37"/>
-    </i>
-    <i>
-      <x v="38"/>
-    </i>
-    <i>
-      <x v="39"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="43"/>
-    </i>
-    <i>
-      <x v="44"/>
-    </i>
-    <i>
-      <x v="45"/>
-    </i>
-    <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
@@ -2474,11 +1778,24 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Monthly_Sales" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Sales" fld="0" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="1">
+  <formats count="4">
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
     <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
   <chartFormats count="1">
@@ -2820,412 +2137,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F76123-E845-48F6-9421-77C779C9BCDE}">
-  <dimension ref="A1:B50"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAF4063-CC69-4491-9C9F-620B355E75CC}">
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>52</v>
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>29958.25</v>
+      <c r="B2" s="1">
+        <v>322100.07</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>25563.98</v>
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1">
+        <v>283455.62</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>33995.57</v>
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>309592.06</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>31587.119999999999</v>
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>286217.15000000002</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>37953.480000000003</v>
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>286779.43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>32008.85</v>
+      <c r="A7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>331116.76</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>30656.27</v>
+      <c r="B8" s="1">
+        <v>277310.18</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>42881.99</v>
+      <c r="A9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1">
+        <v>295651.17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>30369.64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>43646.37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
-        <v>25950.41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>34680.639999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>38351.449999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>53435.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>50828.54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>45747.199999999997</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
-        <v>39215.78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
-        <v>39754.07</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
-        <v>49592.69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
-        <v>48445.34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>49175.79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
-        <v>45347.65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
-        <v>42683.73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25">
-        <v>50446.82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26">
-        <v>57974.76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
-        <v>49206.33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
-        <v>46044.68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
-        <v>38918.300000000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
-        <v>41203.81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
-        <v>48142.95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
-        <v>48445.34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <v>49633.16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34">
-        <v>44890.28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35">
-        <v>43061.440000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36">
-        <v>50069.11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37">
-        <v>38351.449999999997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38">
-        <v>68601.89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39">
-        <v>55131.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40">
-        <v>69261.429999999993</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41">
-        <v>58288.72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42">
-        <v>66996.149999999994</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43">
-        <v>60671.67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44">
-        <v>88590.03</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45">
-        <v>77048.509999999995</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46">
-        <v>71032.14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47">
-        <v>115828.46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48">
-        <v>59762.07</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49">
-        <v>92791.01</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50">
-        <v>2392222.439999999</v>
+      <c r="B10" s="1">
+        <v>2392222.44</v>
       </c>
     </row>
   </sheetData>
@@ -3235,404 +2232,84 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1812109-07FC-4E85-84FC-48C352043FFC}">
-  <dimension ref="A1:B49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B72E6B-2C81-48BB-922F-0C5C53627BBE}">
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4">
-        <v>29958.25</v>
+      <c r="A2" s="1">
+        <v>331116.76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4">
-        <v>25563.98</v>
+      <c r="A3" s="1">
+        <v>322100.07</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4">
-        <v>33995.57</v>
+      <c r="A4" s="1">
+        <v>309592.06</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4">
-        <v>31587.119999999999</v>
+      <c r="A5" s="1">
+        <v>295651.17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4">
-        <v>37953.480000000003</v>
+      <c r="A6" s="1">
+        <v>286779.43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="4">
-        <v>32008.85</v>
+      <c r="A7" s="1">
+        <v>286217.15000000002</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="4">
-        <v>30656.27</v>
+      <c r="A8" s="1">
+        <v>283455.62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="4">
-        <v>42881.99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="4">
-        <v>30369.64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="4">
-        <v>43646.37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="4">
-        <v>25950.41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="4">
-        <v>34680.639999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="4">
-        <v>38351.449999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="4">
-        <v>53435.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4">
-        <v>50828.54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="4">
-        <v>45747.199999999997</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="4">
-        <v>39215.78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="4">
-        <v>39754.07</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="4">
-        <v>49592.69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="4">
-        <v>48445.34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="4">
-        <v>49175.79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="4">
-        <v>45347.65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="4">
-        <v>42683.73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="4">
-        <v>50446.82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="4">
-        <v>57974.76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="4">
-        <v>49206.33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="4">
-        <v>46044.68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="4">
-        <v>38918.300000000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="4">
-        <v>41203.81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="4">
-        <v>48142.95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="4">
-        <v>48445.34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="4">
-        <v>49633.16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="4">
-        <v>44890.28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="4">
-        <v>43061.440000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="4">
-        <v>50069.11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="4">
-        <v>38351.449999999997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="4">
-        <v>68601.89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="4">
-        <v>55131.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="4">
-        <v>69261.429999999993</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="4">
-        <v>58288.72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="4">
-        <v>66996.149999999994</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="4">
-        <v>60671.67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="4">
-        <v>88590.03</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="4">
-        <v>77048.509999999995</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" s="4">
-        <v>71032.14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="4">
-        <v>115828.46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" s="4">
-        <v>59762.07</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="4">
-        <v>92791.01</v>
+      <c r="A9" s="1">
+        <v>277310.18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
